--- a/Phase6.2/quantized (Cleaned)/load_7.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_7.xlsx
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -774,15 +767,7 @@
             <a:sp3d/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="9525">
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
             <c:delete val="1"/>
@@ -2306,13 +2291,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
+        <c:marker val="0"/>
         <c:smooth val="0"/>
-        <c:axId val="961999056"/>
-        <c:axId val="224866237"/>
+        <c:axId val="241336612"/>
+        <c:axId val="829065686"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="961999056"/>
+        <c:axId val="241336612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2323,7 +2308,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="1270" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2353,7 +2338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="224866237"/>
+        <c:crossAx val="829065686"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2361,7 +2346,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="224866237"/>
+        <c:axId val="829065686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2410,7 +2395,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="961999056"/>
+        <c:crossAx val="241336612"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2461,7 +2446,7 @@
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4099,11 +4084,11 @@
         </c:dLbls>
         <c:marker val="0"/>
         <c:smooth val="0"/>
-        <c:axId val="569482312"/>
-        <c:axId val="303243339"/>
+        <c:axId val="822765329"/>
+        <c:axId val="688187684"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="569482312"/>
+        <c:axId val="822765329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4144,7 +4129,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="303243339"/>
+        <c:crossAx val="688187684"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4152,7 +4137,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="303243339"/>
+        <c:axId val="688187684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4186,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="569482312"/>
+        <c:crossAx val="822765329"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4252,7 +4237,7 @@
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4317,31 +4302,9 @@
               <a:t>Inference Program: latency (ms) vs test number</a:t>
             </a:r>
           </a:p>
-          <a:p>
-            <a:pPr defTabSz="914400">
-              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.155328947368421"/>
-          <c:y val="0.0259481037924152"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5897,11 +5860,11 @@
         </c:dLbls>
         <c:marker val="0"/>
         <c:smooth val="0"/>
-        <c:axId val="931486186"/>
-        <c:axId val="571360828"/>
+        <c:axId val="321337075"/>
+        <c:axId val="765756388"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="931486186"/>
+        <c:axId val="321337075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5942,7 +5905,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571360828"/>
+        <c:crossAx val="765756388"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5950,7 +5913,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="571360828"/>
+        <c:axId val="765756388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5999,7 +5962,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="931486186"/>
+        <c:crossAx val="321337075"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6115,21 +6078,6 @@
               <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
             </a:r>
           </a:p>
-          <a:p>
-            <a:pPr defTabSz="914400">
-              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
         </c:rich>
       </c:tx>
       <c:layout/>
@@ -7688,11 +7636,11 @@
         </c:dLbls>
         <c:marker val="0"/>
         <c:smooth val="0"/>
-        <c:axId val="152638321"/>
-        <c:axId val="799458110"/>
+        <c:axId val="388839741"/>
+        <c:axId val="66426781"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="152638321"/>
+        <c:axId val="388839741"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7733,7 +7681,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="799458110"/>
+        <c:crossAx val="66426781"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7741,7 +7689,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="799458110"/>
+        <c:axId val="66426781"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7790,7 +7738,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="152638321"/>
+        <c:crossAx val="388839741"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8030,7 +7978,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10055">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8179,7 +8127,7 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -8187,7 +8135,6 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
-      <a:effectLst/>
     </cs:spPr>
   </cs:dataPointMarker>
   <cs:dataPointMarkerLayout symbol="circle" size="5"/>
@@ -10055,24 +10002,24 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
+      <xdr:colOff>63500</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>147320</xdr:rowOff>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>489585</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>214630</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>102235</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="10" name="Chart 9"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3568700" y="515620"/>
-        <a:ext cx="5264785" cy="2717165"/>
+        <a:off x="3378200" y="400050"/>
+        <a:ext cx="7694930" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -10085,24 +10032,24 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>521335</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>144145</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="11" name="Chart 10"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3836035" y="3543300"/>
-        <a:ext cx="5244465" cy="3414395"/>
+        <a:off x="3390900" y="3219450"/>
+        <a:ext cx="7569200" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -10114,25 +10061,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>87630</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvPr id="12" name="Chart 11"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3949700" y="7270750"/>
-        <a:ext cx="4826000" cy="3181350"/>
+        <a:off x="3403600" y="6057900"/>
+        <a:ext cx="7542530" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -10144,25 +10091,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>107315</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvPr id="13" name="Chart 12"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8953500" y="539750"/>
-        <a:ext cx="4826000" cy="2743200"/>
+        <a:off x="3403600" y="8921750"/>
+        <a:ext cx="7562215" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -17692,7 +17639,7 @@
         <v>595.530989</v>
       </c>
       <c r="D482">
-        <f>A482+B482+C482</f>
+        <f t="shared" ref="D482:D500" si="9">A482+B482+C482</f>
         <v>3687.777463</v>
       </c>
     </row>
@@ -17707,7 +17654,7 @@
         <v>646.015605</v>
       </c>
       <c r="D483">
-        <f>A483+B483+C483</f>
+        <f t="shared" si="9"/>
         <v>4037.535421</v>
       </c>
     </row>
@@ -17722,7 +17669,7 @@
         <v>351.348554</v>
       </c>
       <c r="D484">
-        <f>A484+B484+C484</f>
+        <f t="shared" si="9"/>
         <v>3770.069631</v>
       </c>
     </row>
@@ -17737,7 +17684,7 @@
         <v>702.039434</v>
       </c>
       <c r="D485">
-        <f>A485+B485+C485</f>
+        <f t="shared" si="9"/>
         <v>4147.266487</v>
       </c>
     </row>
@@ -17752,7 +17699,7 @@
         <v>441.282104</v>
       </c>
       <c r="D486">
-        <f>A486+B486+C486</f>
+        <f t="shared" si="9"/>
         <v>4184.889742</v>
       </c>
     </row>
@@ -17767,7 +17714,7 @@
         <v>702.699276</v>
       </c>
       <c r="D487">
-        <f>A487+B487+C487</f>
+        <f t="shared" si="9"/>
         <v>4331.621632</v>
       </c>
     </row>
@@ -17782,7 +17729,7 @@
         <v>549.995626</v>
       </c>
       <c r="D488">
-        <f>A488+B488+C488</f>
+        <f t="shared" si="9"/>
         <v>4384.491223</v>
       </c>
     </row>
@@ -17797,7 +17744,7 @@
         <v>344.289791</v>
       </c>
       <c r="D489">
-        <f>A489+B489+C489</f>
+        <f t="shared" si="9"/>
         <v>4340.723154</v>
       </c>
     </row>
@@ -17812,7 +17759,7 @@
         <v>604.949284</v>
       </c>
       <c r="D490">
-        <f>A490+B490+C490</f>
+        <f t="shared" si="9"/>
         <v>4332.467307</v>
       </c>
     </row>
@@ -17827,7 +17774,7 @@
         <v>696.511366</v>
       </c>
       <c r="D491">
-        <f>A491+B491+C491</f>
+        <f t="shared" si="9"/>
         <v>4395.93693</v>
       </c>
     </row>
@@ -17842,7 +17789,7 @@
         <v>697.124549</v>
       </c>
       <c r="D492">
-        <f>A492+B492+C492</f>
+        <f t="shared" si="9"/>
         <v>4741.978452</v>
       </c>
     </row>
@@ -17857,7 +17804,7 @@
         <v>498.790844</v>
       </c>
       <c r="D493">
-        <f>A493+B493+C493</f>
+        <f t="shared" si="9"/>
         <v>4522.865581</v>
       </c>
     </row>
@@ -17872,7 +17819,7 @@
         <v>750.469618</v>
       </c>
       <c r="D494">
-        <f>A494+B494+C494</f>
+        <f t="shared" si="9"/>
         <v>4830.231427</v>
       </c>
     </row>
@@ -17887,7 +17834,7 @@
         <v>949.165103</v>
       </c>
       <c r="D495">
-        <f>A495+B495+C495</f>
+        <f t="shared" si="9"/>
         <v>5085.406628</v>
       </c>
     </row>
@@ -17902,7 +17849,7 @@
         <v>802.810259</v>
       </c>
       <c r="D496">
-        <f>A496+B496+C496</f>
+        <f t="shared" si="9"/>
         <v>5335.405805</v>
       </c>
     </row>
@@ -17917,7 +17864,7 @@
         <v>748.165023</v>
       </c>
       <c r="D497">
-        <f>A497+B497+C497</f>
+        <f t="shared" si="9"/>
         <v>5744.827553</v>
       </c>
     </row>
@@ -17932,7 +17879,7 @@
         <v>752.113651</v>
       </c>
       <c r="D498">
-        <f>A498+B498+C498</f>
+        <f t="shared" si="9"/>
         <v>5915.863967</v>
       </c>
     </row>
@@ -17947,7 +17894,7 @@
         <v>703.568551</v>
       </c>
       <c r="D499">
-        <f>A499+B499+C499</f>
+        <f t="shared" si="9"/>
         <v>5933.283337</v>
       </c>
     </row>
@@ -17962,7 +17909,7 @@
         <v>693.146478</v>
       </c>
       <c r="D500">
-        <f>A500+B500+C500</f>
+        <f t="shared" si="9"/>
         <v>5932.675273</v>
       </c>
     </row>
